--- a/docs/PP_Preves_V1.xlsx
+++ b/docs/PP_Preves_V1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\tesis-sp-tracking\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835ABF42-DE6A-4E95-880A-9A78418D432B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7047542E-9F61-4E90-A478-403C2FB4B7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan de Prueba" sheetId="3" r:id="rId1"/>
@@ -213,16 +213,6 @@
     <t>Etapa de alimentación (carga y elevación de tensión)</t>
   </si>
   <si>
-    <t>1. Energizar la etapa desde la fuente de laboratorio y luego desde la celda 18650.
-2. Medir la tensión del riel de salida.
-3. Verificar el funcionamiento bajo carga.</t>
-  </si>
-  <si>
-    <t>Fuente de laboratorio
-Celda 18650
-Multímetro</t>
-  </si>
-  <si>
     <t>El riel de salida entrega la tensión especificada y el sistema opera de forma estable.</t>
   </si>
   <si>
@@ -370,17 +360,6 @@
     <t>Integración en protoboard con alimentación real</t>
   </si>
   <si>
-    <t>1. Integrar en protoboard el módulo SD, la placa Adafruit y el módulo A7670SA.
-2. Alimentar con fuente de laboratorio y luego con la celda 18650 y su convertidor elevador.
-3. Ejecutar el ciclo del sistema y ajustar el conexionado.</t>
-  </si>
-  <si>
-    <t>Protoboard
-Fuente de laboratorio
-Celda 18650
-Multímetro</t>
-  </si>
-  <si>
     <t>El sistema opera de forma estable, sirviendo de base para el diseño del PCB.</t>
   </si>
   <si>
@@ -558,9 +537,6 @@
     <t>Se comparó mantener el archivo abierto de forma permanente (más eficiente en velocidad y consumo) frente a abrirlo y cerrarlo en cada escritura. Se adoptó esta última por robustez ante cortes de tensión o vibración. Se eligió el formato CSV por su practicidad para el posprocesamiento.</t>
   </si>
   <si>
-    <t>En proceso de refuerzo: durante las pruebas de transmisión se observó que la línea de alimentación no sostenía los picos de corriente del módulo A7670SA, por lo que se está rediseñando la etapa (celda 18650 y capacitor de 470 µF). Verificar además la tensión real del riel de salida del convertidor elevador.</t>
-  </si>
-  <si>
     <t>Se efectuaron correcciones en el conexionado. Se detectó que el módulo de tarjeta SD requería 5 V únicamente por su propia etapa de regulación; dado que la placa Adafruit y la SD operan de forma nativa a 3,3 V, dicha etapa se eliminó en la versión de PCB. La configuración estable resultante se tomó como base para el diseño del circuito impreso.</t>
   </si>
   <si>
@@ -621,9 +597,6 @@
     <t>Las pruebas se ejecutan de manera incremental: cada módulo se valida de forma aislada (prueba unitaria) antes de integrarlo, y las pruebas de integración y de homologación solo se realizan una vez superadas las etapas previas. Cada caso se registra en la planilla con su procedimiento, resultado esperado, resultado obtenido y observaciones. Ante un resultado no exitoso, se documenta la causa y la corrección aplicada, y la prueba se repite en una nueva iteración hasta su validación.</t>
   </si>
   <si>
-    <t>Simulador de ECU (Arduino con controlador y transceptor CAN), intérprete ELM327, placa Adafruit Feather nRF52840 Sense, módulo A7670SA (GNSS + 4G-LTE), módulo de tarjeta SD, celda 18650 con convertidor elevador, fuente regulada de laboratorio y multímetro. Como herramientas de software: el entorno Arduino IDE y su monitor serie, una aplicación de escaneo Bluetooth serie en el celular, KiCad para el diseño y verificación del PCB, y el servidor con Node-RED para el procesamiento de la telemetría.</t>
-  </si>
-  <si>
     <t>Se definen como ambientes de prueba las distintas configuraciones de hardware y software disponibles en cada instancia de la evaluación, considerando que estas evolucionan a lo largo del desarrollo. Se distinguen tres: el ambiente de laboratorio, sobre plataformas de prototipado (Arduino, protoboard y fuente regulada); el ambiente de banco con el prototipo final alimentado por batería; y el ambiente de campo, con el dispositivo instalado en un vehículo real y transmitiendo al servidor.</t>
   </si>
   <si>
@@ -631,6 +604,33 @@
   </si>
   <si>
     <t>Respuesta a comandos OBD-II estándar via Bluetooth</t>
+  </si>
+  <si>
+    <t>Protoboard
+Fuente de laboratorio
+Celda 103450
+Multímetro</t>
+  </si>
+  <si>
+    <t>1. Energizar la etapa desde la fuente de laboratorio y luego desde la celda 103450.
+2. Medir la tensión del riel de salida.
+3. Verificar el funcionamiento bajo carga.</t>
+  </si>
+  <si>
+    <t>Fuente de laboratorio
+Celda 103450
+Multímetro</t>
+  </si>
+  <si>
+    <t>1. Integrar en protoboard el módulo SD, la placa Adafruit y el módulo A7670SA.
+2. Alimentar con fuente de laboratorio y luego con la celda 103450 y su convertidor elevador.
+3. Ejecutar el ciclo del sistema y ajustar el conexionado.</t>
+  </si>
+  <si>
+    <t>En proceso de refuerzo: durante las pruebas de transmisión se observó que la línea de alimentación no sostenía los picos de corriente del módulo A7670SA, por lo que se está rediseñando la etapa (celda 103450 y capacitor de 470 µF). Verificar además la tensión real del riel de salida del convertidor elevador.</t>
+  </si>
+  <si>
+    <t>Simulador de ECU (Arduino con controlador y transceptor CAN), intérprete ELM327, placa Adafruit Feather nRF52840 Sense, módulo A7670SA (GNSS + 4G-LTE), módulo de tarjeta SD, celda 103450 con convertidor elevador, fuente regulada de laboratorio y multímetro. Como herramientas de software: el entorno Arduino IDE y su monitor serie, una aplicación de escaneo Bluetooth serie en el celular, KiCad para el diseño y verificación del PCB, y el servidor con Node-RED para el procesamiento de la telemetría.</t>
   </si>
 </sst>
 </file>
@@ -745,11 +745,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1061,105 +1061,105 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="A1" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
+      <c r="A2" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
+      <c r="A5" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
     </row>
     <row r="6" spans="1:6" ht="7.5" customHeight="1"/>
     <row r="7" spans="1:6">
-      <c r="A7" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
+      <c r="A7" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
+      <c r="A8" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
+      <c r="A10" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
     </row>
     <row r="14" spans="1:6" ht="217.5">
       <c r="A14" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="188.5">
       <c r="A17" s="4" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="203">
       <c r="A20" s="4" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F20" s="10"/>
     </row>
     <row r="23" spans="1:6" s="2" customFormat="1" ht="188.5">
       <c r="A23" s="4" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="159.5">
       <c r="A26" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -1220,7 +1220,7 @@
       <c r="B2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="8" t="s">
@@ -1243,8 +1243,8 @@
       <c r="B3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>176</v>
+      <c r="C3" s="11" t="s">
+        <v>170</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>10</v>
@@ -1411,13 +1411,13 @@
         <v>32</v>
       </c>
       <c r="E10" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="100" customHeight="1">
@@ -1425,367 +1425,367 @@
         <v>24</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="100" customHeight="1">
       <c r="A12" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>63</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E12" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>64</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="100" customHeight="1">
       <c r="A13" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E13" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="100" customHeight="1">
       <c r="A14" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="100" customHeight="1">
       <c r="A15" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="100" customHeight="1">
       <c r="A16" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="100" customHeight="1">
       <c r="A17" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="E17" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="F17" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="G17" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="100" customHeight="1">
       <c r="A18" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>90</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>92</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E18" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="G18" s="8" t="s">
         <v>93</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="100" customHeight="1">
       <c r="A19" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="100" customHeight="1">
       <c r="A20" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="100" customHeight="1">
       <c r="A21" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="F21" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="G21" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="100" customHeight="1">
       <c r="A22" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B22" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G22" s="8" t="s">
         <v>118</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="100" customHeight="1">
       <c r="A23" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B23" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="G23" s="8" t="s">
         <v>123</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="100" customHeight="1">
       <c r="A24" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B24" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G24" s="8" t="s">
         <v>128</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="100" customHeight="1">
       <c r="A25" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="100" customHeight="1">
       <c r="A26" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B26" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F26" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="G26" s="8" t="s">
         <v>139</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -1834,10 +1834,10 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="100" customHeight="1">
@@ -1863,10 +1863,10 @@
         <v>13</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="100" customHeight="1">
@@ -1892,10 +1892,10 @@
         <v>18</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="100" customHeight="1">
@@ -1921,10 +1921,10 @@
         <v>23</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="100" customHeight="1">
@@ -1950,10 +1950,10 @@
         <v>29</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="100" customHeight="1">
@@ -1979,10 +1979,10 @@
         <v>35</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="100" customHeight="1">
@@ -2008,10 +2008,10 @@
         <v>40</v>
       </c>
       <c r="H7" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>146</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="100" customHeight="1">
@@ -2037,10 +2037,10 @@
         <v>45</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="100" customHeight="1">
@@ -2066,10 +2066,10 @@
         <v>50</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="100" customHeight="1">
@@ -2086,19 +2086,19 @@
         <v>32</v>
       </c>
       <c r="E10" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>55</v>
-      </c>
       <c r="H10" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="100" customHeight="1">
@@ -2106,492 +2106,492 @@
         <v>24</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>60</v>
-      </c>
       <c r="H11" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="100" customHeight="1">
       <c r="A12" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>63</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E12" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>66</v>
-      </c>
       <c r="H12" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="100" customHeight="1">
       <c r="A13" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E13" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>71</v>
-      </c>
       <c r="H13" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="100" customHeight="1">
       <c r="A14" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="100" customHeight="1">
       <c r="A15" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="100" customHeight="1">
       <c r="A16" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="100" customHeight="1">
       <c r="A17" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="E17" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="F17" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="G17" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>89</v>
-      </c>
       <c r="H17" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="100" customHeight="1">
       <c r="A18" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>90</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>92</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E18" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="G18" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>95</v>
-      </c>
       <c r="H18" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="100" customHeight="1">
       <c r="A19" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="100" customHeight="1">
       <c r="A20" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="100" customHeight="1">
       <c r="A21" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B21" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="G21" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>111</v>
-      </c>
       <c r="H21" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="100" customHeight="1">
       <c r="A22" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="F22" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="G22" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>117</v>
-      </c>
       <c r="H22" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="100" customHeight="1">
       <c r="A23" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B23" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G23" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>122</v>
-      </c>
       <c r="H23" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="100" customHeight="1">
       <c r="A24" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B24" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="G24" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>127</v>
-      </c>
       <c r="H24" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="100" customHeight="1">
       <c r="A25" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B25" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G25" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>132</v>
-      </c>
       <c r="H25" s="8" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="100" customHeight="1">
       <c r="A26" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="100" customHeight="1">
       <c r="A27" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B27" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F27" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="G27" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="D27" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="F27" s="8" t="s">
+      <c r="H27" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="G27" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>146</v>
-      </c>
       <c r="I27" s="8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
